--- a/Data/CSV/StageGravity.xlsx
+++ b/Data/CSV/StageGravity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Class\VocationalSchoolData\Programing\SpringContest\SpringContest_26\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7338DA0E-3C94-459D-9DC5-CB62A6959A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2E3F3A-58F5-48CA-8C03-65E9CBE6F9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>重力ステージ１(前)</t>
   </si>
@@ -49,6 +49,22 @@
   </si>
   <si>
     <t>重力ステージ４(後ろ)</t>
+  </si>
+  <si>
+    <t>重力ステージ5(前)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重力ステージ5(後ろ)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重力ステージ6(前)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重力ステージ6(後ろ)</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -100,16 +116,50 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="16">
     <dxf>
       <font>
         <color theme="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFA50000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor auto="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="dashDot">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -128,6 +178,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF005500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA50000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -181,7 +241,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF8A0000"/>
+          <bgColor rgb="FF005500"/>
         </patternFill>
       </fill>
     </dxf>
@@ -191,21 +251,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -215,168 +261,9 @@
       </font>
       <fill>
         <patternFill>
-          <fgColor auto="1"/>
-          <bgColor theme="1"/>
+          <bgColor rgb="FFA50000"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="dashDot">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="dashDot">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="dashDot">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="dashDot">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -665,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:W72"/>
   <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="16384" width="3.08203125" style="1"/>
@@ -766,6 +653,9 @@
       <c r="M3" s="1">
         <v>0</v>
       </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
       <c r="S3" s="1">
         <v>0</v>
       </c>
@@ -801,8 +691,11 @@
       <c r="M4" s="1">
         <v>0</v>
       </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
       <c r="Q4" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R4" s="1">
         <v>0</v>
@@ -827,6 +720,9 @@
       <c r="M5" s="1">
         <v>0</v>
       </c>
+      <c r="O5" s="1">
+        <v>6</v>
+      </c>
       <c r="W5" s="1">
         <v>0</v>
       </c>
@@ -857,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
@@ -888,12 +784,12 @@
       <c r="M7" s="1">
         <v>0</v>
       </c>
-      <c r="N7" s="1">
-        <v>6</v>
-      </c>
       <c r="R7" s="1">
         <v>3</v>
       </c>
+      <c r="S7" s="1">
+        <v>4</v>
+      </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
@@ -926,6 +822,9 @@
       <c r="M8" s="1">
         <v>0</v>
       </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
       <c r="P8" s="1">
         <v>0</v>
       </c>
@@ -958,11 +857,8 @@
       <c r="M9" s="1">
         <v>0</v>
       </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
+      <c r="Q9" s="1">
+        <v>6</v>
       </c>
       <c r="W9" s="1">
         <v>0</v>
@@ -987,6 +883,9 @@
       <c r="M10" s="1">
         <v>0</v>
       </c>
+      <c r="T10" s="1">
+        <v>6</v>
+      </c>
       <c r="U10" s="1">
         <v>0</v>
       </c>
@@ -1008,6 +907,12 @@
         <v>0</v>
       </c>
       <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
         <v>0</v>
       </c>
       <c r="W11" s="1">
@@ -1209,13 +1114,13 @@
         <v>0</v>
       </c>
       <c r="B17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
         <v>4</v>
@@ -1224,10 +1129,10 @@
         <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -1247,7 +1152,13 @@
     </row>
     <row r="18" spans="1:23">
       <c r="A18" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>6</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -1273,7 +1184,10 @@
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -1285,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -1308,7 +1222,7 @@
     </row>
     <row r="20" spans="1:23">
       <c r="A20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
@@ -1316,8 +1230,8 @@
       <c r="F20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="1">
-        <v>4</v>
+      <c r="G20" s="1">
+        <v>6</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -1340,22 +1254,7 @@
     </row>
     <row r="21" spans="1:23">
       <c r="A21" s="1">
-        <v>4</v>
-      </c>
-      <c r="D21" s="1">
-        <v>4</v>
-      </c>
-      <c r="E21" s="1">
-        <v>4</v>
-      </c>
-      <c r="F21" s="1">
-        <v>4</v>
-      </c>
-      <c r="G21" s="1">
-        <v>4</v>
-      </c>
-      <c r="H21" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -1375,10 +1274,10 @@
     </row>
     <row r="22" spans="1:23">
       <c r="A22" s="1">
-        <v>4</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>6</v>
       </c>
       <c r="K22" s="1">
         <v>0</v>
@@ -1398,7 +1297,19 @@
     </row>
     <row r="23" spans="1:23">
       <c r="A23" s="1">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="B23" s="1">
+        <v>5</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>5</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -2018,7 +1929,7 @@
         <v>4</v>
       </c>
       <c r="J39" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -2127,6 +2038,9 @@
       <c r="A43" s="1">
         <v>0</v>
       </c>
+      <c r="D43" s="1">
+        <v>6</v>
+      </c>
       <c r="K43" s="1">
         <v>0</v>
       </c>
@@ -2345,32 +2259,1087 @@
         <v>0</v>
       </c>
     </row>
+    <row r="49" spans="1:23">
+      <c r="A49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23">
+      <c r="A50" s="1">
+        <v>0</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="1">
+        <v>0</v>
+      </c>
+      <c r="V50" s="1">
+        <v>0</v>
+      </c>
+      <c r="W50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23">
+      <c r="A51" s="1">
+        <v>0</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="O51" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+      <c r="T51" s="1">
+        <v>2</v>
+      </c>
+      <c r="U51" s="1">
+        <v>0</v>
+      </c>
+      <c r="V51" s="1">
+        <v>0</v>
+      </c>
+      <c r="W51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23">
+      <c r="A52" s="1">
+        <v>0</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+      <c r="U52" s="1">
+        <v>0</v>
+      </c>
+      <c r="V52" s="1">
+        <v>0</v>
+      </c>
+      <c r="W52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23">
+      <c r="A53" s="1">
+        <v>0</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+      <c r="U53" s="1">
+        <v>0</v>
+      </c>
+      <c r="V53" s="1">
+        <v>0</v>
+      </c>
+      <c r="W53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23">
+      <c r="A54" s="1">
+        <v>0</v>
+      </c>
+      <c r="D54" s="1">
+        <v>6</v>
+      </c>
+      <c r="G54" s="1">
+        <v>3</v>
+      </c>
+      <c r="K54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+      <c r="S54" s="1">
+        <v>0</v>
+      </c>
+      <c r="U54" s="1">
+        <v>0</v>
+      </c>
+      <c r="V54" s="1">
+        <v>0</v>
+      </c>
+      <c r="W54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23">
+      <c r="A55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="1">
+        <v>6</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="1">
+        <v>6</v>
+      </c>
+      <c r="W55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23">
+      <c r="A56" s="1">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1">
+        <v>0</v>
+      </c>
+      <c r="C56" s="1">
+        <v>0</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="1">
+        <v>6</v>
+      </c>
+      <c r="W56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23">
+      <c r="A57" s="1">
+        <v>0</v>
+      </c>
+      <c r="B57" s="1">
+        <v>0</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="O57" s="1">
+        <v>4</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="U57" s="1">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
+        <v>0</v>
+      </c>
+      <c r="W57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23">
+      <c r="A58" s="1">
+        <v>0</v>
+      </c>
+      <c r="B58" s="1">
+        <v>0</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>0</v>
+      </c>
+      <c r="O58" s="1">
+        <v>4</v>
+      </c>
+      <c r="P58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0</v>
+      </c>
+      <c r="U58" s="1">
+        <v>0</v>
+      </c>
+      <c r="V58" s="1">
+        <v>0</v>
+      </c>
+      <c r="W58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23">
+      <c r="A59" s="1">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <v>2</v>
+      </c>
+      <c r="K59" s="1">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1">
+        <v>0</v>
+      </c>
+      <c r="O59" s="1">
+        <v>5</v>
+      </c>
+      <c r="P59" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+      <c r="U59" s="1">
+        <v>0</v>
+      </c>
+      <c r="V59" s="1">
+        <v>0</v>
+      </c>
+      <c r="W59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23">
+      <c r="A60" s="1">
+        <v>0</v>
+      </c>
+      <c r="B60" s="1">
+        <v>0</v>
+      </c>
+      <c r="C60" s="1">
+        <v>0</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0</v>
+      </c>
+      <c r="U60" s="1">
+        <v>0</v>
+      </c>
+      <c r="V60" s="1">
+        <v>0</v>
+      </c>
+      <c r="W60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23">
+      <c r="A61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23">
+      <c r="A62" s="1">
+        <v>0</v>
+      </c>
+      <c r="B62" s="1">
+        <v>0</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
+        <v>0</v>
+      </c>
+      <c r="O62" s="1">
+        <v>0</v>
+      </c>
+      <c r="P62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>0</v>
+      </c>
+      <c r="R62" s="1">
+        <v>0</v>
+      </c>
+      <c r="S62" s="1">
+        <v>0</v>
+      </c>
+      <c r="T62" s="1">
+        <v>0</v>
+      </c>
+      <c r="U62" s="1">
+        <v>0</v>
+      </c>
+      <c r="V62" s="1">
+        <v>0</v>
+      </c>
+      <c r="W62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23">
+      <c r="A63" s="1">
+        <v>0</v>
+      </c>
+      <c r="B63" s="1">
+        <v>1</v>
+      </c>
+      <c r="J63" s="1">
+        <v>2</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>5</v>
+      </c>
+      <c r="U63" s="1">
+        <v>0</v>
+      </c>
+      <c r="V63" s="1">
+        <v>2</v>
+      </c>
+      <c r="W63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23">
+      <c r="A64" s="1">
+        <v>0</v>
+      </c>
+      <c r="B64" s="1">
+        <v>0</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <v>0</v>
+      </c>
+      <c r="O64" s="1">
+        <v>0</v>
+      </c>
+      <c r="P64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>0</v>
+      </c>
+      <c r="R64" s="1">
+        <v>4</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1">
+        <v>0</v>
+      </c>
+      <c r="W64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23">
+      <c r="A65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1">
+        <v>0</v>
+      </c>
+      <c r="O65" s="1">
+        <v>4</v>
+      </c>
+      <c r="P65" s="1">
+        <v>6</v>
+      </c>
+      <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="1">
+        <v>0</v>
+      </c>
+      <c r="W65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23">
+      <c r="A66" s="1">
+        <v>0</v>
+      </c>
+      <c r="C66" s="1">
+        <v>0</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0</v>
+      </c>
+      <c r="O66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
+      </c>
+      <c r="U66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23">
+      <c r="A67" s="1">
+        <v>0</v>
+      </c>
+      <c r="C67" s="1">
+        <v>4</v>
+      </c>
+      <c r="F67" s="1">
+        <v>3</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1">
+        <v>0</v>
+      </c>
+      <c r="O67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>0</v>
+      </c>
+      <c r="R67" s="1">
+        <v>3</v>
+      </c>
+      <c r="S67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="1">
+        <v>0</v>
+      </c>
+      <c r="W67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23">
+      <c r="A68" s="1">
+        <v>0</v>
+      </c>
+      <c r="C68" s="1">
+        <v>4</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>4</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23">
+      <c r="A69" s="1">
+        <v>0</v>
+      </c>
+      <c r="C69" s="1">
+        <v>0</v>
+      </c>
+      <c r="D69" s="1">
+        <v>6</v>
+      </c>
+      <c r="I69" s="1">
+        <v>4</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
+        <v>0</v>
+      </c>
+      <c r="O69" s="1">
+        <v>0</v>
+      </c>
+      <c r="R69" s="1">
+        <v>5</v>
+      </c>
+      <c r="U69" s="1">
+        <v>0</v>
+      </c>
+      <c r="W69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23">
+      <c r="A70" s="1">
+        <v>0</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0</v>
+      </c>
+      <c r="D70" s="1">
+        <v>4</v>
+      </c>
+      <c r="E70" s="1">
+        <v>4</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="M70" s="1">
+        <v>0</v>
+      </c>
+      <c r="O70" s="1">
+        <v>0</v>
+      </c>
+      <c r="P70" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>0</v>
+      </c>
+      <c r="R70" s="1">
+        <v>4</v>
+      </c>
+      <c r="S70" s="1">
+        <v>0</v>
+      </c>
+      <c r="T70" s="1">
+        <v>0</v>
+      </c>
+      <c r="U70" s="1">
+        <v>0</v>
+      </c>
+      <c r="W70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23">
+      <c r="A71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1">
+        <v>0</v>
+      </c>
+      <c r="W71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23">
+      <c r="A72" s="1">
+        <v>0</v>
+      </c>
+      <c r="B72" s="1">
+        <v>0</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1">
+        <v>0</v>
+      </c>
+      <c r="O72" s="1">
+        <v>0</v>
+      </c>
+      <c r="P72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1">
+        <v>0</v>
+      </c>
+      <c r="S72" s="1">
+        <v>0</v>
+      </c>
+      <c r="T72" s="1">
+        <v>0</v>
+      </c>
+      <c r="U72" s="1">
+        <v>0</v>
+      </c>
+      <c r="V72" s="1">
+        <v>0</v>
+      </c>
+      <c r="W72" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="7" priority="7">
+  <conditionalFormatting sqref="A1:XFD6 A7:M7 O7:XFD7">
+    <cfRule type="cellIs" dxfId="15" priority="33" operator="equal">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="34" operator="equal">
+      <formula>4</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="35" operator="equal">
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="39">
       <formula>MOD(ROW(),12)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="11" priority="40">
       <formula>AND(A1=0,A1&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="41" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="42" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="43" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:XFD1048576">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>6</formula>
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>MOD(ROW(),12)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>AND(A8=0,A8&lt;&gt;"")</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
